--- a/名古屋_提出物/建築_提出物リスト.xlsx
+++ b/名古屋_提出物/建築_提出物リスト.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t xml:space="preserve">名古屋_提出物管理リスト（建築のみ）</t>
   </si>
@@ -632,6 +632,164 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">階ピット図</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">B棟</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">階平面詳細図</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Revit)★</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">改修</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K)メディカル棟平面詳細図(STEP4-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)AW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)ELV鉄骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)アルミハニカムパネル庇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)エレベータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)エントランス外部敷石割付図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)キャノピー基礎伏図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)キャノピー鉄骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)シャッター下埋込みアングル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)トイレブース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)トイレ家具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)パスボックス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)メディカル棟平面詳細図(STEP4-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)リングブロア室・産廃置場改修図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)リングブロア室タラップ・手摺・鋼製床製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)リングブロア室他シャッター製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)リングブロア室他鉄骨製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)リングブロア室他内外部SD製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)外壁ALC製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)間仕切り下地製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)既存東2-3間AW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)既存南側小庇上水切</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)既存梁補強鉄骨製作図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)竪樋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)男子トイレ汚垂石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)柱型ステンレスパネル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)内部SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改)防煙垂れ壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外構</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外)外構図</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">システム天井パネル工事施工計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現場発泡ウレタン吹付工事施工計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エアシャワー工事施工計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">件数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">B</t>
     </r>
     <r>
@@ -642,173 +800,6 @@
       </rPr>
       <t xml:space="preserve">棟</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階平面詳細図</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Revit)★</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">改修</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">K)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">メディカル棟平面詳細図</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(STEP4-5)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">改)AW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)ELV鉄骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)アルミハニカムパネル庇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)エレベータ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)エントランス外部敷石割付図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)キャノピー基礎伏図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)キャノピー鉄骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)シャッター下埋込みアングル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)トイレブース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)トイレ家具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)パスボックス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)メディカル棟平面詳細図(STEP4-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室・産廃置場改修図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室タラップ・手摺・鋼製床製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室他シャッター製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室他鉄骨製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室他内外部SD製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)外壁ALC製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)間仕切り下地製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存東2-3間AW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存南側小庇上水切</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存梁補強鉄骨製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)竪樋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)男子トイレ汚垂石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)柱型ステンレスパネル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)内部SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)防煙垂れ壁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外構</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外)外構図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">システム天井パネル工事施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現場発泡ウレタン吹付工事施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エアシャワー工事施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1階ピット図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">件数</t>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -896,10 +887,9 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,19 +929,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDED"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE4DFEC"/>
         <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -1004,7 +988,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1049,6 +1033,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1061,14 +1049,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1093,22 +1081,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1118,6 +1090,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1130,7 +1106,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1167,14 +1143,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFEDEDED"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1246,9 +1214,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFEDEDED"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1720,412 +1688,412 @@
       <c r="D23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="14"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>29</v>
+      <c r="B26" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="14"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>29</v>
+      <c r="B27" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="14"/>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>29</v>
+      <c r="B28" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="14"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>29</v>
+      <c r="B29" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="14"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="n">
+      <c r="A30" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>29</v>
+      <c r="B30" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="14"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>29</v>
+      <c r="B31" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="14"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>29</v>
+      <c r="B32" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="14"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>29</v>
+      <c r="B33" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="14"/>
+      <c r="D33" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>29</v>
+      <c r="A34" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="14"/>
+      <c r="D34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>29</v>
+      <c r="B35" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="14"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="n">
+      <c r="A36" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>29</v>
+      <c r="B36" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="14"/>
+      <c r="D36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>29</v>
+      <c r="B37" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="14"/>
+      <c r="D37" s="16"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>29</v>
+      <c r="B38" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="14"/>
+      <c r="D38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>29</v>
+      <c r="B39" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="14"/>
+      <c r="D39" s="16"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="n">
+      <c r="A40" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>29</v>
+      <c r="B40" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="14"/>
+      <c r="D40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>29</v>
+      <c r="B41" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="14"/>
+      <c r="D41" s="16"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="13" t="s">
-        <v>29</v>
+      <c r="B42" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="14"/>
+      <c r="D42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>29</v>
+      <c r="B43" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="14"/>
+      <c r="D43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12" t="n">
+      <c r="A44" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>29</v>
+      <c r="B44" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="14"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>29</v>
+      <c r="B45" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="14"/>
+      <c r="D45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="n">
+      <c r="A46" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>29</v>
+      <c r="B46" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="14"/>
+      <c r="D46" s="16"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>29</v>
+      <c r="B47" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="14"/>
+      <c r="D47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="n">
+      <c r="A48" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="13" t="s">
-        <v>29</v>
+      <c r="B48" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D48" s="14"/>
+      <c r="D48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="n">
+      <c r="A49" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>29</v>
+      <c r="B49" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="14"/>
+      <c r="D49" s="16"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="n">
+      <c r="A50" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>29</v>
+      <c r="B50" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="14"/>
+      <c r="D50" s="16"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="13" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>29</v>
+      <c r="B51" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="14"/>
+      <c r="D51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>29</v>
+      <c r="B52" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D52" s="14"/>
+      <c r="D52" s="16"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="n">
+      <c r="A53" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="D53" s="15"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D53" s="18"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="D54" s="19"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D54" s="21"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D55" s="21"/>
+      <c r="D55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="n">
+      <c r="A56" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>60</v>
+      <c r="B56" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="C56" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D56" s="21"/>
+      <c r="D56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="23" t="n">
+      <c r="A57" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D57" s="25"/>
+      <c r="D57" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:D57"/>
@@ -2157,80 +2125,75 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="26" t="n">
+      <c r="B2" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A2)</f>
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="26" t="n">
+      <c r="B3" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A3)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="26" t="n">
+      <c r="A4" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="26" t="n">
+      <c r="A5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A5)</f>
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="26" t="n">
+      <c r="A6" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A6)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="26" t="n">
+      <c r="A7" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A7)</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="26" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A8)</f>
-        <v>1</v>
+      <c r="A8" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <f aca="false">SUM(B2:B7)</f>
+        <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="28" t="n">
-        <f aca="false">SUM(B2:B8)</f>
-        <v>53</v>
-      </c>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/名古屋_提出物/建築_提出物リスト.xlsx
+++ b/名古屋_提出物/建築_提出物リスト.xlsx
@@ -12,7 +12,7 @@
     <sheet name="区分別件数" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">建築_提出物リスト!$A$4:$D$57</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">建築_提出物リスト!$A$4:$D$54</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
   <si>
     <t xml:space="preserve">名古屋_提出物管理リスト（建築のみ）</t>
   </si>
   <si>
-    <t xml:space="preserve">出典：700_名古屋_075739_FSRM_2024（スクリーンショット 2026/10/12時点）。設備（機械・電気・設備共通）は除外。K)は改修として分類。</t>
+    <t xml:space="preserve">出典：700_名古屋_075739_FSRM_2024（スクリーンショット 2026/10/12 11:55時点）。設備（機械・電気・設備共通）は除外。K)は改修として分類。</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -211,7 +211,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">受付カウンター</t>
+      <t xml:space="preserve">竪樋</t>
     </r>
   </si>
   <si>
@@ -230,7 +230,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">竪樋</t>
+      <t xml:space="preserve">竪樋養生管</t>
     </r>
   </si>
   <si>
@@ -249,7 +249,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">竪樋養生管</t>
+      <t xml:space="preserve">内部</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">製作図</t>
     </r>
   </si>
   <si>
@@ -277,7 +294,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AW</t>
+      <t xml:space="preserve">SD</t>
     </r>
     <r>
       <rPr>
@@ -304,7 +321,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">内部</t>
+      <t xml:space="preserve">内部サイン</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部追加</t>
     </r>
     <r>
       <rPr>
@@ -315,14 +351,6 @@
       </rPr>
       <t xml:space="preserve">SD</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">製作図</t>
-    </r>
   </si>
   <si>
     <r>
@@ -340,53 +368,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">内部サイン</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">内部追加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SD</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">北</t>
     </r>
     <r>
@@ -644,7 +625,26 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">B棟</t>
+    <t xml:space="preserve">最新スクショの範囲外（未確認）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">棟</t>
+    </r>
   </si>
   <si>
     <r>
@@ -678,10 +678,32 @@
     <t xml:space="preserve">改修</t>
   </si>
   <si>
-    <t xml:space="preserve">K)メディカル棟平面詳細図(STEP4-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)AW</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">メディカル棟平面詳細図</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(STEP4-5)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">改)ELV鉄骨</t>
@@ -729,9 +751,6 @@
     <t xml:space="preserve">改)リングブロア室他鉄骨製作図</t>
   </si>
   <si>
-    <t xml:space="preserve">改)リングブロア室他内外部SD製作図</t>
-  </si>
-  <si>
     <t xml:space="preserve">改)外壁ALC製作図</t>
   </si>
   <si>
@@ -781,25 +800,6 @@
   </si>
   <si>
     <t xml:space="preserve">件数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">棟</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -887,6 +887,7 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -988,7 +989,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1029,14 +1030,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1049,14 +1050,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1069,6 +1070,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1081,6 +1086,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1093,7 +1114,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1616,23 +1637,23 @@
       <c r="D17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="7"/>
+      <c r="C18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>22</v>
@@ -1644,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>23</v>
@@ -1656,7 +1677,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>24</v>
@@ -1668,7 +1689,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>25</v>
@@ -1680,36 +1701,38 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="12"/>
+      <c r="B25" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="n">
@@ -1718,10 +1741,10 @@
       <c r="B26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="16"/>
+      <c r="C26" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="n">
@@ -1730,10 +1753,10 @@
       <c r="B27" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="16"/>
+      <c r="C27" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="n">
@@ -1742,10 +1765,10 @@
       <c r="B28" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="n">
@@ -1754,10 +1777,10 @@
       <c r="B29" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="16"/>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="n">
@@ -1766,10 +1789,10 @@
       <c r="B30" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="16"/>
+      <c r="C30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="n">
@@ -1778,10 +1801,10 @@
       <c r="B31" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="16"/>
+      <c r="C31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="n">
@@ -1790,10 +1813,10 @@
       <c r="B32" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="16"/>
+      <c r="C32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="n">
@@ -1802,10 +1825,10 @@
       <c r="B33" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="16"/>
+      <c r="C33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="n">
@@ -1814,10 +1837,10 @@
       <c r="B34" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="16"/>
+      <c r="C34" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="n">
@@ -1826,10 +1849,10 @@
       <c r="B35" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="16"/>
+      <c r="C35" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="n">
@@ -1838,10 +1861,10 @@
       <c r="B36" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="16"/>
+      <c r="C36" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="n">
@@ -1850,10 +1873,10 @@
       <c r="B37" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="16"/>
+      <c r="C37" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="n">
@@ -1862,10 +1885,10 @@
       <c r="B38" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="16"/>
+      <c r="C38" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="n">
@@ -1874,10 +1897,10 @@
       <c r="B39" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="16"/>
+      <c r="C39" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="n">
@@ -1886,10 +1909,10 @@
       <c r="B40" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="16"/>
+      <c r="C40" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="n">
@@ -1898,10 +1921,10 @@
       <c r="B41" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="16"/>
+      <c r="C41" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="15"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="n">
@@ -1910,10 +1933,10 @@
       <c r="B42" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C42" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="16"/>
+      <c r="C42" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="15"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="n">
@@ -1922,10 +1945,10 @@
       <c r="B43" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="16"/>
+      <c r="C43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="n">
@@ -1934,10 +1957,10 @@
       <c r="B44" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="16"/>
+      <c r="C44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="15"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="n">
@@ -1946,10 +1969,10 @@
       <c r="B45" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="16"/>
+      <c r="C45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="n">
@@ -1958,10 +1981,10 @@
       <c r="B46" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D46" s="16"/>
+      <c r="C46" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="15"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="n">
@@ -1970,10 +1993,10 @@
       <c r="B47" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="16"/>
+      <c r="C47" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="15"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="n">
@@ -1982,10 +2005,10 @@
       <c r="B48" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="16"/>
+      <c r="C48" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="n">
@@ -1994,10 +2017,10 @@
       <c r="B49" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="16"/>
+      <c r="C49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="n">
@@ -2006,97 +2029,83 @@
       <c r="B50" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="16"/>
+      <c r="C50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="17" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="16"/>
+      <c r="B51" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="16"/>
+      <c r="B52" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="21" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D53" s="15"/>
+      <c r="B53" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="n">
+      <c r="A54" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" s="19"/>
+      <c r="C54" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="23"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="22"/>
+      <c r="A55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="22"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" s="22"/>
+      <c r="A57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D57"/>
+  <autoFilter ref="A4:D54"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2125,75 +2134,75 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A2)</f>
-        <v>14</v>
+      <c r="B2" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A2)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A3)</f>
+      <c r="A3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A3)</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A4)</f>
+      <c r="A4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A5)</f>
-        <v>28</v>
+      <c r="A5" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A5)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A6)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="23" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$57,A7)</f>
+      <c r="B7" s="28" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A7)</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="30" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/名古屋_提出物/建築_提出物リスト.xlsx
+++ b/名古屋_提出物/建築_提出物リスト.xlsx
@@ -12,7 +12,7 @@
     <sheet name="区分別件数" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">建築_提出物リスト!$A$4:$D$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">建築_提出物リスト!$A$4:$D$51</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
   <si>
     <t xml:space="preserve">名古屋_提出物管理リスト（建築のみ）</t>
   </si>
@@ -613,28 +613,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階ピット図</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最新スクショの範囲外（未確認）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">B</t>
     </r>
     <r>
@@ -706,94 +684,773 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">改)ELV鉄骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)アルミハニカムパネル庇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)エレベータ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)エントランス外部敷石割付図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)キャノピー基礎伏図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)キャノピー鉄骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)シャッター下埋込みアングル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)トイレブース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)トイレ家具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)パスボックス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)メディカル棟平面詳細図(STEP4-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室・産廃置場改修図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室タラップ・手摺・鋼製床製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室他シャッター製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)リングブロア室他鉄骨製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)外壁ALC製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)間仕切り下地製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存東2-3間AW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存南側小庇上水切</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)既存梁補強鉄骨製作図</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)竪樋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)男子トイレ汚垂石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)柱型ステンレスパネル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)内部SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改)防煙垂れ壁</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)ELV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鉄骨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アルミハニカムパネル庇</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">エレベータ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">エントランス外部敷石割付図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キャノピー基礎伏図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キャノピー鉄骨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シャッター下埋込みアングル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トイレブース</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トイレ家具</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パスボックス</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">メディカル棟平面詳細図</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(STEP4-2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リングブロア室・産廃置場改修図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リングブロア室タラップ・手摺・鋼製床製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リングブロア室他シャッター製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リングブロア室他鉄骨製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外壁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ALC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間仕切り下地製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存東</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AW</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存南側小庇上水切</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存梁補強鉄骨製作図</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">竪樋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">男子トイレ汚垂石</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">柱型ステンレスパネル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">防煙垂れ壁</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">外構</t>
   </si>
   <si>
-    <t xml:space="preserve">外)外構図</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外構図</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">システム天井パネル工事施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現場発泡ウレタン吹付工事施工計画書</t>
   </si>
   <si>
     <t xml:space="preserve">エアシャワー工事施工計画書</t>
@@ -989,7 +1646,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1030,10 +1687,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1046,7 +1699,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1054,7 +1707,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1062,15 +1715,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1078,12 +1727,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1697,415 +2342,391 @@
       <c r="D22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="B24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="B30" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="B31" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="14" t="s">
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="B34" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="D25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="D26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B36" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="B37" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="D28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="B38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B39" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="B40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="D31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="n">
+      <c r="B41" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="C41" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="D32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="B42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="D34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="B44" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B45" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="15"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B46" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="D37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B47" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="D38" s="15"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="D39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="B49" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="D40" s="15"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B50" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="18"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="19" t="n">
         <v>47</v>
       </c>
-      <c r="D41" s="15"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="15"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="15"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="15"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="15"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="15"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="15"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" s="15"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="15"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="15"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D51" s="20"/>
+      <c r="D51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="A52" s="22"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>27</v>
-      </c>
+      <c r="A53" s="22"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="23"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="25"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="25"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="25"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D54"/>
+  <autoFilter ref="A4:D51"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2134,75 +2755,75 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A2)</f>
+      <c r="B2" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A2)</f>
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A3)</f>
-        <v>6</v>
+      <c r="B3" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A3)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A4)</f>
+      <c r="B5" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A5)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A6)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A5)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A6)</f>
+      <c r="B7" s="25" t="n">
+        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$51,A7)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="28" t="n">
-        <f aca="false">COUNTIF(建築_提出物リスト!$B$5:$B$54,A7)</f>
-        <v>3</v>
-      </c>
-    </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="30" t="n">
+      <c r="A8" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="27" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
